--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeAsset.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeAsset.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23231"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78DF504-0CF8-4253-B688-E58D7B739E1F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2775" windowWidth="12495" windowHeight="3105"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>批复号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -42,14 +42,34 @@
   </si>
   <si>
     <t>到期日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>授信对象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>授信总份额（亿份）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否循环额度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>附件条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否持有至到期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,12 +117,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -144,7 +167,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -176,9 +199,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -210,6 +251,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -385,24 +444,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
     <col min="2" max="2" width="13.75" customWidth="1"/>
     <col min="3" max="3" width="19.75" customWidth="1"/>
     <col min="4" max="4" width="26.125" customWidth="1"/>
-    <col min="5" max="6" width="12.125" customWidth="1"/>
-    <col min="7" max="7" width="20.875" customWidth="1"/>
-    <col min="8" max="8" width="19.25" customWidth="1"/>
-    <col min="9" max="9" width="17.25" customWidth="1"/>
-    <col min="10" max="10" width="19.25" customWidth="1"/>
-    <col min="11" max="11" width="18.25" customWidth="1"/>
-    <col min="12" max="12" width="15.625" customWidth="1"/>
+    <col min="5" max="9" width="12.125" customWidth="1"/>
+    <col min="10" max="10" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.125" customWidth="1"/>
+    <col min="12" max="12" width="20.875" customWidth="1"/>
+    <col min="13" max="13" width="19.25" customWidth="1"/>
+    <col min="14" max="14" width="17.25" customWidth="1"/>
+    <col min="15" max="15" width="19.25" customWidth="1"/>
+    <col min="16" max="16" width="18.25" customWidth="1"/>
+    <col min="17" max="17" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -422,6 +483,21 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
         <v>2</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeAsset.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/CeAsset.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78DF504-0CF8-4253-B688-E58D7B739E1F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>批复号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -62,13 +61,17 @@
   </si>
   <si>
     <t>是否持有至到期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -125,7 +128,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -200,23 +203,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -252,23 +238,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -444,26 +413,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
     <col min="2" max="2" width="13.75" customWidth="1"/>
     <col min="3" max="3" width="19.75" customWidth="1"/>
     <col min="4" max="4" width="26.125" customWidth="1"/>
-    <col min="5" max="9" width="12.125" customWidth="1"/>
-    <col min="10" max="10" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.125" customWidth="1"/>
-    <col min="12" max="12" width="20.875" customWidth="1"/>
-    <col min="13" max="13" width="19.25" customWidth="1"/>
-    <col min="14" max="14" width="17.25" customWidth="1"/>
-    <col min="15" max="15" width="19.25" customWidth="1"/>
-    <col min="16" max="16" width="18.25" customWidth="1"/>
-    <col min="17" max="17" width="15.625" customWidth="1"/>
+    <col min="5" max="10" width="12.125" customWidth="1"/>
+    <col min="11" max="11" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.125" customWidth="1"/>
+    <col min="13" max="13" width="20.875" customWidth="1"/>
+    <col min="14" max="14" width="19.25" customWidth="1"/>
+    <col min="15" max="15" width="17.25" customWidth="1"/>
+    <col min="16" max="16" width="19.25" customWidth="1"/>
+    <col min="17" max="17" width="18.25" customWidth="1"/>
+    <col min="18" max="18" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -489,15 +458,18 @@
         <v>8</v>
       </c>
       <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>2</v>
       </c>
     </row>
